--- a/new-stats/botev-vratsa.xlsx
+++ b/new-stats/botev-vratsa.xlsx
@@ -1699,22 +1699,58 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>28/02/2026</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Botev Vratsa</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Beroe</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
+      <c r="M24" t="n">
+        <v>9</v>
+      </c>
+      <c r="N24" t="n">
+        <v>2</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>

--- a/new-stats/botev-vratsa.xlsx
+++ b/new-stats/botev-vratsa.xlsx
@@ -1753,40 +1753,112 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>04/03/2026</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>CSKA Sofia</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Botev Vratsa</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1</v>
+      </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
+      <c r="M25" t="n">
+        <v>4</v>
+      </c>
+      <c r="N25" t="n">
+        <v>20</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>07/03/2026</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Botev Vratsa</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Arda</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
+      <c r="M26" t="n">
+        <v>5</v>
+      </c>
+      <c r="N26" t="n">
+        <v>5</v>
+      </c>
+      <c r="O26" t="n">
+        <v>2</v>
+      </c>
+      <c r="P26" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>

--- a/new-stats/botev-vratsa.xlsx
+++ b/new-stats/botev-vratsa.xlsx
@@ -1861,22 +1861,58 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr"/>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>14/03/2026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Botev Plovdiv</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>3</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Botev Vratsa</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" t="n">
+        <v>2</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
+      <c r="M27" t="n">
+        <v>11</v>
+      </c>
+      <c r="N27" t="n">
+        <v>15</v>
+      </c>
+      <c r="O27" t="n">
+        <v>7</v>
+      </c>
+      <c r="P27" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>

--- a/new-stats/botev-vratsa.xlsx
+++ b/new-stats/botev-vratsa.xlsx
@@ -1915,22 +1915,58 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>22/03/2026</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Botev Vratsa</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Lok. Plovdiv</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1</v>
+      </c>
+      <c r="J28" t="n">
+        <v>2</v>
+      </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
+      <c r="M28" t="n">
+        <v>9</v>
+      </c>
+      <c r="N28" t="n">
+        <v>8</v>
+      </c>
+      <c r="O28" t="n">
+        <v>3</v>
+      </c>
+      <c r="P28" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>

--- a/new-stats/botev-vratsa.xlsx
+++ b/new-stats/botev-vratsa.xlsx
@@ -619,22 +619,58 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>02/08/2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ludogorets</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Botev Vratsa</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
+      <c r="M4" t="n">
+        <v>7</v>
+      </c>
+      <c r="N4" t="n">
+        <v>9</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2</v>
+      </c>
+      <c r="P4" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>

--- a/new-stats/botev-vratsa.xlsx
+++ b/new-stats/botev-vratsa.xlsx
@@ -673,40 +673,112 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Botev Vratsa</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Slavia Sofia</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3</v>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
+      <c r="M5" t="n">
+        <v>11</v>
+      </c>
+      <c r="N5" t="n">
+        <v>6</v>
+      </c>
+      <c r="O5" t="n">
+        <v>3</v>
+      </c>
+      <c r="P5" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>16/08/2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CSKA Sofia</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Botev Vratsa</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3</v>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
+      <c r="M6" t="n">
+        <v>11</v>
+      </c>
+      <c r="N6" t="n">
+        <v>19</v>
+      </c>
+      <c r="O6" t="n">
+        <v>4</v>
+      </c>
+      <c r="P6" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
